--- a/data/trans_dic/IQ2606_R2-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ2606_R2-Habitat-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,32 +625,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59,42%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>70,45%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>84,46%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>55,78%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>70,77%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>85,48%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>70,45%</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>85,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>85,07%</t>
+          <t>84,96%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>48,14; 62,75</t>
+          <t>52,72; 65,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>63,37; 77,12</t>
+          <t>63,37; 76,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72,86; 93,02</t>
+          <t>70,96; 92,71</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>52,43; 65,83</t>
+          <t>48,14; 63,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>64,21; 77,03</t>
+          <t>63,3; 76,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,23; 92,91</t>
+          <t>73,65; 93,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>52,91; 62,29</t>
+          <t>52,37; 62,39</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>65,9; 75,46</t>
+          <t>65,33; 75,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>76,57; 91,08</t>
+          <t>75,8; 91,07</t>
         </is>
       </c>
     </row>
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>54,58%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>69,8%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88,16%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>63,77%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>71,53%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>78,06%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>54,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>69,8%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>78,2%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>84,37%</t>
+          <t>84,17%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>57,85; 68,85</t>
+          <t>49,69; 60,63</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>65,98; 76,57</t>
+          <t>64,88; 75,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>65,06; 88,21</t>
+          <t>79,85; 93,92</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49,1; 60,21</t>
+          <t>58,21; 69,31</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,3; 74,64</t>
+          <t>66,37; 75,99</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>79,71; 93,81</t>
+          <t>63,81; 87,86</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>54,93; 62,71</t>
+          <t>54,96; 62,77</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>67,05; 74,11</t>
+          <t>67,01; 74,23</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>77,22; 90,23</t>
+          <t>76,45; 89,83</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>63,69%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>77,83%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>89,02%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>65,56%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>78,82%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>89,11%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>77,83%</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>59,28; 71,2</t>
+          <t>57,66; 69,74</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>73,66; 83,79</t>
+          <t>72,26; 82,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>77,33; 96,4</t>
+          <t>77,43; 95,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,24; 69,94</t>
+          <t>58,88; 71,7</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>72,4; 82,71</t>
+          <t>73,24; 83,17</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>77,24; 95,18</t>
+          <t>73,29; 95,09</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60,21; 68,92</t>
+          <t>60,34; 68,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>74,28; 81,87</t>
+          <t>74,2; 81,94</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>81,2; 94,04</t>
+          <t>80,69; 93,62</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>54,65%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>75,79%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>80,27%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>62,26%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>71,72%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>83,87%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>54,65%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>75,79%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>82,27%</t>
+          <t>81,07%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>56,6; 68,46</t>
+          <t>48,41; 60,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,24; 76,94</t>
+          <t>70,55; 80,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73,4; 91,73</t>
+          <t>66,17; 89,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>48,09; 60,16</t>
+          <t>56,24; 67,76</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,82; 80,08</t>
+          <t>66,04; 76,76</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,66; 89,34</t>
+          <t>70,62; 88,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>54,46; 62,59</t>
+          <t>54,0; 62,66</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>70,03; 77,62</t>
+          <t>70,35; 77,48</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73,47; 88,25</t>
+          <t>73,54; 87,37</t>
         </is>
       </c>
     </row>
@@ -1065,32 +1065,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>57,57%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>73,38%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>85,67%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>62,12%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>73,05%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>83,69%</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>57,57%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>73,38%</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>85,7%</t>
+          <t>82,74%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>84,84%</t>
+          <t>84,39%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>59,02; 65,05</t>
+          <t>54,13; 60,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>70,32; 75,94</t>
+          <t>70,58; 76,08</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>78,18; 88,21</t>
+          <t>80,69; 89,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54,57; 60,63</t>
+          <t>58,64; 64,89</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>70,62; 75,96</t>
+          <t>69,98; 75,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>80,75; 89,91</t>
+          <t>77,03; 87,75</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,72; 62,13</t>
+          <t>57,37; 61,76</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>71,07; 75,01</t>
+          <t>71,28; 75,11</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>81,58; 87,88</t>
+          <t>80,46; 87,75</t>
         </is>
       </c>
     </row>
@@ -1216,14 +1216,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1311,32 +1311,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>103</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>130</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>42</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>137</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>87952</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>103787</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>27425</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>76967</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>92819</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>23246</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>87952</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>103787</t>
-        </is>
-      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>29864</t>
+          <t>23727</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>53110</t>
+          <t>51152</t>
         </is>
       </c>
     </row>
@@ -1417,47 +1417,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>66435; 86598</t>
+          <t>78027; 97354</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>83118; 101146</t>
+          <t>93356; 113313</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>19814; 25296</t>
+          <t>23042; 30103</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>77603; 97430</t>
+          <t>66433; 87066</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>94596; 113476</t>
+          <t>83021; 100202</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25802; 32736</t>
+          <t>20428; 25925</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>151338; 178150</t>
+          <t>149766; 178434</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>183522; 210125</t>
+          <t>181918; 209386</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>47802; 56862</t>
+          <t>45636; 54831</t>
         </is>
       </c>
     </row>
@@ -1474,32 +1474,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>198</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>238</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>49</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
@@ -1527,32 +1527,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>118846</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>154343</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>51832</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>126677</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>146483</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>30689</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>118846</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>154343</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55224</t>
+          <t>30784</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>85913</t>
+          <t>82616</t>
         </is>
       </c>
     </row>
@@ -1580,47 +1580,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>114906; 136769</t>
+          <t>108184; 132011</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>135119; 156810</t>
+          <t>143456; 165978</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>25579; 34680</t>
+          <t>46943; 55215</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>106904; 131089</t>
+          <t>115619; 137682</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>142179; 165046</t>
+          <t>135912; 155627</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>49834; 58648</t>
+          <t>25119; 34585</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>228713; 261121</t>
+          <t>228825; 261363</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>285588; 315652</t>
+          <t>285419; 316160</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78637; 91889</t>
+          <t>75044; 88174</t>
         </is>
       </c>
     </row>
@@ -1637,32 +1637,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>154</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>39</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>193</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1690,32 +1690,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>100495</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>128818</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>36951</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>98642</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>120548</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>26929</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>100495</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>128818</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>39008</t>
+          <t>23962</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1730,7 +1730,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>65937</t>
+          <t>60913</t>
         </is>
       </c>
     </row>
@@ -1743,47 +1743,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>89195; 107131</t>
+          <t>90978; 110044</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>112659; 128158</t>
+          <t>119596; 137271</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>23369; 29134</t>
+          <t>32138; 39485</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90314; 110356</t>
+          <t>88592; 107881</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>119822; 136895</t>
+          <t>112016; 127211</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>34130; 42057</t>
+          <t>19992; 25938</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>185587; 212439</t>
+          <t>185984; 212029</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>236560; 260708</t>
+          <t>236280; 260942</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>60419; 69975</t>
+          <t>55500; 64396</t>
         </is>
       </c>
     </row>
@@ -1800,32 +1800,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>168</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>200</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>56</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>217</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1853,32 +1853,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>110360</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>153647</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>36599</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>126148</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>146777</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>38364</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>110360</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>153647</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>40259</t>
+          <t>36468</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1893,7 +1893,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>78623</t>
+          <t>73067</t>
         </is>
       </c>
     </row>
@@ -1906,47 +1906,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>114681; 138716</t>
+          <t>97754; 121455</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>135553; 157459</t>
+          <t>143016; 162644</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>33574; 41957</t>
+          <t>30169; 40606</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>97107; 121499</t>
+          <t>113958; 137291</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>143571; 162341</t>
+          <t>135143; 157081</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34713; 44517</t>
+          <t>31453; 39535</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>220317; 253226</t>
+          <t>218458; 253498</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>285262; 316187</t>
+          <t>286596; 315633</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>70212; 84340</t>
+          <t>66282; 78745</t>
         </is>
       </c>
     </row>
@@ -1963,32 +1963,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>596</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>778</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>623</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>768</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>186</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>596</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>778</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -2016,32 +2016,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>417652</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>540595</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>152806</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
           <t>428434</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr">
         <is>
           <t>506627</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>119227</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>417652</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>540595</t>
-        </is>
-      </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>164355</t>
+          <t>114941</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>283582</t>
+          <t>267748</t>
         </is>
       </c>
     </row>
@@ -2069,47 +2069,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>407089; 448689</t>
+          <t>392687; 437154</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>487730; 526672</t>
+          <t>519925; 560415</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111389; 125669</t>
+          <t>143923; 160044</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>395913; 439847</t>
+          <t>404431; 447552</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>520202; 559587</t>
+          <t>485312; 524695</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>154849; 172418</t>
+          <t>107006; 121901</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>816773; 879233</t>
+          <t>811897; 874003</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>1016482; 1072821</t>
+          <t>1019468; 1074166</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>272672; 293736</t>
+          <t>255275; 278403</t>
         </is>
       </c>
     </row>
